--- a/data/dike_connections.xlsx
+++ b/data/dike_connections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositories\asphalt-db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E907DEDB-91F5-43E1-9B70-9EE3F1D17731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B96CC08-48BA-4B73-A7DE-550CDE3C5863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -336,10 +336,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -647,1152 +646,1145 @@
   <dimension ref="A1:CI87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="32.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="39.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="38.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="25.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="25.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="24.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" customWidth="1"/>
-    <col min="34" max="34" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="45.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="35.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="41.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="29.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="30.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="45.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="53.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="53.42578125" style="1" customWidth="1"/>
-    <col min="62" max="64" width="53.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="36.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="36.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="40.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="39.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="28" style="1" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="51.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="32.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="54.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="55.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="37.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="30.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="80" max="82" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="43.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="45.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="88" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="38" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="33" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" customWidth="1"/>
+    <col min="34" max="34" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="35" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="26" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="32" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="53.42578125" customWidth="1"/>
+    <col min="62" max="64" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="20" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="28" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="80" max="82" width="31" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="23" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="21" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="45.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>55</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>50</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>8</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>12</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>51</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>52</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>80</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>40</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AF1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG1" t="s">
         <v>84</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>13</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>31</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>6</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>45</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>82</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>72</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>2</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>26</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>75</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>22</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>67</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>20</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>16</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>10</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>64</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>17</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>3</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>59</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" t="s">
         <v>83</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" t="s">
         <v>11</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>85</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>86</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>47</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>48</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>49</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>41</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>69</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" t="s">
         <v>81</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>36</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>74</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>73</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" t="s">
         <v>4</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" t="s">
         <v>44</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" t="s">
         <v>23</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" t="s">
         <v>60</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" t="s">
         <v>61</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" t="s">
         <v>63</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" t="s">
         <v>62</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" t="s">
         <v>57</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" t="s">
         <v>53</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" t="s">
         <v>34</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" t="s">
         <v>33</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" t="s">
         <v>32</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" t="s">
         <v>35</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" t="s">
         <v>21</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" t="s">
         <v>66</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CH1" t="s">
         <v>5</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1">
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>56</v>
       </c>
-      <c r="M14" s="1">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="O15" s="1">
-        <v>1</v>
-      </c>
-      <c r="P15" s="1">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>55</v>
       </c>
-      <c r="O16" s="1">
-        <v>1</v>
-      </c>
-      <c r="P16" s="1">
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>27</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="R18" s="1">
+      <c r="R18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>50</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="T20" s="1">
+      <c r="T20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>15</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="1">
+      <c r="V22">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>12</v>
       </c>
-      <c r="W23" s="1">
+      <c r="W23">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>51</v>
       </c>
-      <c r="X24" s="1">
+      <c r="X24">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>52</v>
       </c>
-      <c r="Y25" s="1">
+      <c r="Y25">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>80</v>
       </c>
-      <c r="Z26" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="1">
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AC26">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>37</v>
       </c>
-      <c r="AA27" s="1">
+      <c r="AA27">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>38</v>
       </c>
-      <c r="AB28" s="1">
+      <c r="AB28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>39</v>
       </c>
-      <c r="Z29" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="1">
+      <c r="Z29">
+        <v>1</v>
+      </c>
+      <c r="AC29">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>40</v>
       </c>
-      <c r="AD30" s="1">
+      <c r="AD30">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="AE31" s="1">
+      <c r="AE31">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="1">
+      <c r="A32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF32">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>84</v>
       </c>
-      <c r="AG33" s="1">
+      <c r="AG33">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>13</v>
       </c>
-      <c r="AH34" s="1">
+      <c r="AH34">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>65</v>
       </c>
-      <c r="AI35" s="1">
+      <c r="AI35">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>31</v>
       </c>
-      <c r="AJ36" s="1">
-        <v>1</v>
-      </c>
-      <c r="AK36" s="1">
-        <v>1</v>
-      </c>
-      <c r="AL36" s="1">
+      <c r="AJ36">
+        <v>1</v>
+      </c>
+      <c r="AK36">
+        <v>1</v>
+      </c>
+      <c r="AL36">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>6</v>
       </c>
-      <c r="AJ37" s="1">
-        <v>1</v>
-      </c>
-      <c r="AK37" s="1">
-        <v>1</v>
-      </c>
-      <c r="AL37" s="1">
+      <c r="AJ37">
+        <v>1</v>
+      </c>
+      <c r="AK37">
+        <v>1</v>
+      </c>
+      <c r="AL37">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>45</v>
       </c>
-      <c r="AJ38" s="1">
-        <v>1</v>
-      </c>
-      <c r="AK38" s="1">
-        <v>1</v>
-      </c>
-      <c r="AL38" s="1">
+      <c r="AJ38">
+        <v>1</v>
+      </c>
+      <c r="AK38">
+        <v>1</v>
+      </c>
+      <c r="AL38">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>82</v>
       </c>
-      <c r="AM39" s="1">
+      <c r="AM39">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>72</v>
       </c>
-      <c r="AN40" s="1">
+      <c r="AN40">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>2</v>
       </c>
-      <c r="AO41" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP41" s="1">
+      <c r="AO41">
+        <v>1</v>
+      </c>
+      <c r="AP41">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>30</v>
       </c>
-      <c r="AO42" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP42" s="1">
+      <c r="AO42">
+        <v>1</v>
+      </c>
+      <c r="AP42">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>26</v>
       </c>
-      <c r="AQ43" s="1">
+      <c r="AQ43">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>75</v>
       </c>
-      <c r="AR44" s="1">
+      <c r="AR44">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>22</v>
       </c>
-      <c r="AS45" s="1">
-        <v>1</v>
-      </c>
-      <c r="AT45" s="1">
+      <c r="AS45">
+        <v>1</v>
+      </c>
+      <c r="AT45">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>67</v>
       </c>
-      <c r="AS46" s="1">
-        <v>1</v>
-      </c>
-      <c r="AT46" s="1">
+      <c r="AS46">
+        <v>1</v>
+      </c>
+      <c r="AT46">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>20</v>
       </c>
-      <c r="AU47" s="1">
+      <c r="AU47">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>9</v>
       </c>
-      <c r="AV48" s="1">
+      <c r="AV48">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>16</v>
       </c>
-      <c r="AW49" s="1">
+      <c r="AW49">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>10</v>
       </c>
-      <c r="AX50" s="1">
+      <c r="AX50">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>64</v>
       </c>
-      <c r="AY51" s="1">
+      <c r="AY51">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>17</v>
       </c>
-      <c r="AZ52" s="1">
+      <c r="AZ52">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>54</v>
       </c>
-      <c r="BA53" s="1">
+      <c r="BA53">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>43</v>
       </c>
-      <c r="BB54" s="1">
+      <c r="BB54">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>3</v>
       </c>
-      <c r="BC55" s="1">
+      <c r="BC55">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>59</v>
       </c>
-      <c r="BD56" s="1">
+      <c r="BD56">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>83</v>
       </c>
-      <c r="BE57" s="1">
+      <c r="BE57">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>11</v>
       </c>
-      <c r="BF58" s="1">
+      <c r="BF58">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>46</v>
       </c>
-      <c r="BG59" s="1">
+      <c r="BG59">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>85</v>
       </c>
-      <c r="BH60" s="1">
+      <c r="BH60">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>86</v>
       </c>
-      <c r="BI61" s="1">
+      <c r="BI61">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>47</v>
       </c>
-      <c r="BJ62" s="1">
+      <c r="BJ62">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>48</v>
       </c>
-      <c r="BK63" s="1">
+      <c r="BK63">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>49</v>
       </c>
-      <c r="BL64" s="1">
+      <c r="BL64">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>41</v>
       </c>
-      <c r="BM65" s="1">
+      <c r="BM65">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>69</v>
       </c>
-      <c r="BN66" s="1">
+      <c r="BN66">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>81</v>
       </c>
-      <c r="BO67" s="1">
-        <v>1</v>
-      </c>
-      <c r="BS67" s="1">
-        <v>1</v>
-      </c>
-      <c r="BT67" s="1">
+      <c r="BO67">
+        <v>1</v>
+      </c>
+      <c r="BS67">
+        <v>1</v>
+      </c>
+      <c r="BT67">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>36</v>
       </c>
-      <c r="BP68" s="1">
-        <v>1</v>
-      </c>
-      <c r="BR68" s="1">
+      <c r="BP68">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>74</v>
       </c>
-      <c r="BQ69" s="1">
+      <c r="BQ69">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>73</v>
       </c>
-      <c r="BP70" s="1">
-        <v>1</v>
-      </c>
-      <c r="BR70" s="1">
+      <c r="BR70">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>4</v>
       </c>
-      <c r="BO71" s="1">
-        <v>1</v>
-      </c>
-      <c r="BS71" s="1">
-        <v>1</v>
-      </c>
-      <c r="BT71" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB71" s="1">
-        <v>1</v>
-      </c>
-      <c r="CC71" s="1">
-        <v>1</v>
-      </c>
-      <c r="CD71" s="1">
+      <c r="BO71">
+        <v>1</v>
+      </c>
+      <c r="BS71">
+        <v>1</v>
+      </c>
+      <c r="BT71">
+        <v>1</v>
+      </c>
+      <c r="CB71">
+        <v>1</v>
+      </c>
+      <c r="CC71">
+        <v>1</v>
+      </c>
+      <c r="CD71">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>44</v>
       </c>
-      <c r="BO72" s="1">
-        <v>1</v>
-      </c>
-      <c r="BS72" s="1">
-        <v>1</v>
-      </c>
-      <c r="BT72" s="1">
-        <v>1</v>
-      </c>
-      <c r="CD72" s="1">
+      <c r="BO72">
+        <v>1</v>
+      </c>
+      <c r="BS72">
+        <v>1</v>
+      </c>
+      <c r="BT72">
+        <v>1</v>
+      </c>
+      <c r="CD72">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>23</v>
       </c>
-      <c r="BU73" s="1">
+      <c r="BU73">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>60</v>
       </c>
-      <c r="BV74" s="1">
+      <c r="BV74">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>61</v>
       </c>
-      <c r="BW75" s="1">
+      <c r="BW75">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>63</v>
       </c>
-      <c r="BX76" s="1">
+      <c r="BX76">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>62</v>
       </c>
-      <c r="BY77" s="1">
+      <c r="BY77">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>57</v>
       </c>
-      <c r="BZ78" s="1">
+      <c r="BZ78">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>53</v>
       </c>
-      <c r="CA79" s="1">
+      <c r="CA79">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>34</v>
       </c>
-      <c r="BS80" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB80" s="1">
+      <c r="BS80">
+        <v>1</v>
+      </c>
+      <c r="CB80">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>33</v>
       </c>
-      <c r="BS81" s="1">
-        <v>1</v>
-      </c>
-      <c r="CC81" s="1">
+      <c r="BS81">
+        <v>1</v>
+      </c>
+      <c r="CC81">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>32</v>
       </c>
-      <c r="BS82" s="1">
-        <v>1</v>
-      </c>
-      <c r="BT82" s="1">
-        <v>1</v>
-      </c>
-      <c r="CD82" s="1">
+      <c r="BS82">
+        <v>1</v>
+      </c>
+      <c r="BT82">
+        <v>1</v>
+      </c>
+      <c r="CD82">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>35</v>
       </c>
-      <c r="CE83" s="1">
+      <c r="CE83">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>21</v>
       </c>
-      <c r="CF84" s="1">
-        <v>1</v>
-      </c>
-      <c r="CG84" s="1">
+      <c r="CF84">
+        <v>1</v>
+      </c>
+      <c r="CG84">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>66</v>
       </c>
-      <c r="CF85" s="1">
-        <v>1</v>
-      </c>
-      <c r="CG85" s="1">
+      <c r="CF85">
+        <v>1</v>
+      </c>
+      <c r="CG85">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>5</v>
       </c>
-      <c r="CH86" s="1">
+      <c r="CH86">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:87" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>42</v>
       </c>
-      <c r="CI87" s="1">
+      <c r="CI87">
         <v>1</v>
       </c>
     </row>
